--- a/stories/arbres/TREE-REL-007.xlsx
+++ b/stories/arbres/TREE-REL-007.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Dans le salon, un enfant rit d'un dessin de Sami. Léa entend le rire. Sami baisse la tête. Maman est près du canapé. Papa range des livres. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Dans le salon, un enfant rit d'un dessin de Sami. Léa entend le rire. Sami baisse la tête. Maman est près du canapé. Papa range des livres. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Dans le salon, un enfant rit d'un dessin de Sami. Léa entend le rire. Sami baisse la tête. Maman est près du canapé. Papa range des livres. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Près du chat, un rire pas gentil part. C'est le chat. Un cube tape un autre cube, doucement. Léa s'approche, sans courir. Papa n'est pas loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Près du chat, un rire pas gentil part. C'est le chat. Un cube tape un autre cube, doucement. Léa s'approche, sans courir. Papa n'est pas loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Près du chat, un rire pas gentil part. C'est le chat. Un cube tape un autre cube, doucement. Léa s'approche, sans courir. Papa n'est pas loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1827,6 +1861,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Quelqu'un rit d'un camarade. Que fait-on ? Avec le chat.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1851,7 +1890,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa retient le geste. Elle respire.</t>
+          <t>Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa retient le geste. Elle respire.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1993,6 +2032,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa retient le geste. Elle respire.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2225,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2203,7 +2254,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le bac à sable, après le chat. La corbeille craque. On parle du bac à sable. Léa écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi le bac à sable, après le chat. La corbeille craque. On parle du bac à sable. Léa écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2341,6 +2392,12 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le bac à sable, après le chat. La corbeille craque. On parle du bac à sable. Léa écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2588,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2555,7 +2617,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après le chat et le bac à sable. La tasse est encore tiède. On dit merci. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa garde le rouge un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+          <t>Léa rejoint le rouge, après le chat et le bac à sable. La tasse est encore tiède. On dit merci. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa garde le rouge un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2693,6 +2755,13 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après le chat et le bac à sable. La tasse est encore tiède. On dit merci. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa garde le rouge un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2924,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2879,7 +2953,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après le chat et le bac à sable. Le parquet craque un tout petit peu. On écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. On écoute le silence une seconde. Léa est assise. On gardu geste.</t>
+          <t>Léa rejoint le bleu, après le chat et le bac à sable. Le parquet craque un tout petit peu. On écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. On écoute le silence une seconde. Léa est assise. On gardu geste.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3017,6 +3091,13 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après le chat et le bac à sable. Le parquet craque un tout petit peu. On écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide. On écoute le silence une seconde.
+narrateur|Léa est assise. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3260,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3203,7 +3289,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après le chat et le bac à sable. Une abeille bourdonne loin. On attend un petit moment. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
+          <t>Léa rejoint le vert, après le chat et le bac à sable. Une abeille bourdonne loin. On attend un petit moment. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3341,6 +3427,13 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après le chat et le bac à sable. Une abeille bourdonne loin. On attend un petit moment. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3596,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3527,7 +3625,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le toboggan, après le chat. La fenêtre tremble un tout petit peu. Léa touche le toboggan tout doucement. Maman dit : je suis là. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi le toboggan, après le chat. La fenêtre tremble un tout petit peu. Léa touche le toboggan tout doucement. Je suis là. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3665,6 +3763,13 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le toboggan, après le chat. La fenêtre tremble un tout petit peu. Léa touche le toboggan tout doucement.
+maman|Je suis là. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3960,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3989,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après le chat et le toboggan. Un gravier roule sous une semelle. On pose les fesses sur une chaise. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa dit merci à maman. Papa sourit. On respire.</t>
+          <t>Léa rejoint le rouge, après le chat et le toboggan. Un gravier roule sous une semelle. On pose les fesses sur une chaise. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa dit merci à maman. Papa sourit. On respire.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4127,13 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après le chat et le toboggan. Un gravier roule sous une semelle. On pose les fesses sur une chaise. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa dit merci à maman. Papa sourit. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4296,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4203,7 +4325,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après le chat et le toboggan. La fenêtre tremble un tout petit peu. On sourit un peu. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. On laisse bleu à sa place. Léa est près de maman. Merci, et au dodo bientôt.</t>
+          <t>Léa rejoint le bleu, après le chat et le toboggan. La fenêtre tremble un tout petit peu. On sourit un peu. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. On laisse bleu à sa place. Léa est près de maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4341,6 +4463,13 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après le chat et le toboggan. La fenêtre tremble un tout petit peu. On sourit un peu. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide. On laisse bleu à sa place.
+narrateur|Léa est près de maman. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4632,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4661,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après le chat et le toboggan. Ça sent le savon de maman. On boit une gorgée d'eau. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+          <t>Léa rejoint le vert, après le chat et le toboggan. Ça sent le savon de maman. On boit une gorgée d'eau. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4799,13 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après le chat et le toboggan. Ça sent le savon de maman. On boit une gorgée d'eau. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4968,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4851,7 +4997,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi les balançoires, après le chat. La pomme est croquante. Léa montre les balançoires à maman. Elle nomme ce qu'elle sent. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi les balançoires, après le chat. La pomme est croquante. Léa montre les balançoires à maman. Elle nomme ce qu'elle sent. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4989,6 +5135,12 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi les balançoires, après le chat. La pomme est croquante. Léa montre les balançoires à maman. Elle nomme ce qu'elle sent. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5331,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5203,7 +5360,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après le chat et les balançoires. Un pigeon roucoule. On essuie une miette. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Maman dit : je t'ai entendu. Papa aussi. On se serre un peu.</t>
+          <t>Léa rejoint le rouge, après le chat et les balançoires. Un pigeon roucoule. On essuie une miette. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5341,6 +5498,13 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après le chat et les balançoires. Un pigeon roucoule. On essuie une miette. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5667,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5527,7 +5696,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après le chat et les balançoires. La cuillère tinte. On referme un livre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa pose bleu et va vers maman. On rentre.</t>
+          <t>Léa rejoint le bleu, après le chat et les balançoires. La cuillère tinte. On referme un livre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa pose bleu et va vers maman. On rentre.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5665,6 +5834,13 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après le chat et les balançoires. La cuillère tinte. On referme un livre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa pose bleu et va vers maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +6003,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5851,7 +6032,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après le chat et les balançoires. Le ballon est un peu poudreux. On pose un jouet à sa place. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa garde le vert un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
+          <t>Léa rejoint le vert, après le chat et les balançoires. Le ballon est un peu poudreux. On pose un jouet à sa place. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa garde le vert un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5989,6 +6170,13 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après le chat et les balançoires. Le ballon est un peu poudreux. On pose un jouet à sa place. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa garde le vert un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6339,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6368,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Près du chien, un rire pas gentil part. Léa s'occupe du chien. Le pain croustille. Maman sourit. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Près du chien, un rire pas gentil part. Léa s'occupe du chien. Le pain croustille. Maman sourit. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6506,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Près du chien, un rire pas gentil part. Léa s'occupe du chien. Le pain croustille. Maman sourit. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6491,6 +6690,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Quelqu'un rit d'un camarade. Que fait-on ? Avec le chien.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6515,7 +6719,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa répète le mot. Maman hoche la tête.</t>
+          <t>Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6657,6 +6861,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa répète le mot. Maman hoche la tête.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7054,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6867,7 +7083,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le bac à sable, après le chien. Un galet est lisse dans la main. On continue avec le bac à sable. Léa gardu geste sûr. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi le bac à sable, après le chien. Un galet est lisse dans la main. On continue avec le bac à sable. Léa gardu geste sûr. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7005,6 +7221,12 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le bac à sable, après le chien. Un galet est lisse dans la main. On continue avec le bac à sable. Léa gardu geste sûr. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7417,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7446,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après le chien et le bac à sable. Une goutte de pluie sèche déjà. On marche tout doucement. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. On se dit à plus tard.</t>
+          <t>Léa rejoint le rouge, après le chien et le bac à sable. Une goutte de pluie sèche déjà. On marche tout doucement. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7584,13 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après le chien et le bac à sable. Une goutte de pluie sèche déjà. On marche tout doucement. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa serre la main de maman, tout doux. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7753,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7543,7 +7782,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après le chien et le bac à sable. Le banc est tiède. On se tait une seconde. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa garde le bleu un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+          <t>Léa rejoint le bleu, après le chien et le bac à sable. Le banc est tiède. On se tait une seconde. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa garde le bleu un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7681,6 +7920,13 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après le chien et le bac à sable. Le banc est tiède. On se tait une seconde. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa garde le bleu un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8089,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7867,7 +8118,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après le chien et le bac à sable. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa dit merci à maman. Papa sourit. On gardu geste.</t>
+          <t>Léa rejoint le vert, après le chien et le bac à sable. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa dit merci à maman. Papa sourit. On gardu geste.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8005,6 +8256,13 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après le chien et le bac à sable. Ça sent le savon des mains. On ouvre les mains, loin de l'autre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa dit merci à maman. Papa sourit. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8425,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8191,7 +8454,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le toboggan, après le chien. Une plume vole. On parle du toboggan. Léa écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi le toboggan, après le chien. Une plume vole. On parle du toboggan. Léa écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8329,6 +8592,12 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le toboggan, après le chien. Une plume vole. On parle du toboggan. Léa écoute jusqu'au bout. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8788,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8543,7 +8817,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après le chien et le toboggan. Une feuille tourne et tombe. On s'assoit près de l'adulte. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
+          <t>Léa rejoint le rouge, après le chien et le toboggan. Une feuille tourne et tombe. On s'assoit près de l'adulte. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8681,6 +8955,13 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après le chien et le toboggan. Une feuille tourne et tombe. On s'assoit près de l'adulte. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9124,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8867,7 +9153,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après le chien et le toboggan. L'eau fait un tout petit bruit. On nomme ce qu'on sent. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa boit une gorgée. Elle se sent plus légère. On respire.</t>
+          <t>Léa rejoint le bleu, après le chien et le toboggan. L'eau fait un tout petit bruit. On nomme ce qu'on sent. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa boit une gorgée. Elle se sent plus légère. On respire.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9005,6 +9291,13 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après le chien et le toboggan. L'eau fait un tout petit bruit. On nomme ce qu'on sent. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa boit une gorgée. Elle se sent plus légère. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9460,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9191,7 +9489,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après le chien et le toboggan. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa garde le vert un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
+          <t>Léa rejoint le vert, après le chien et le toboggan. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa garde le vert un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9329,6 +9627,13 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après le chien et le toboggan. Le soleil chauffe un peu le nez. On reprend le jeu, plus calme. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa garde le vert un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9796,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9515,7 +9825,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi les balançoires, après le chien. Une cloche sonne au loin. On continue avec les balançoires. Léa gardu geste sûr. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi les balançoires, après le chien. Une cloche sonne au loin. On continue avec les balançoires. Léa gardu geste sûr. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9653,6 +9963,12 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi les balançoires, après le chien. Une cloche sonne au loin. On continue avec les balançoires. Léa gardu geste sûr. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10159,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9867,7 +10188,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après le chien et les balançoires. Une plume vole. On range les chaussures. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa pose rouge et va vers maman. Le jeu peut recommencer.</t>
+          <t>Léa rejoint le rouge, après le chien et les balançoires. Une plume vole. On range les chaussures. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa pose rouge et va vers maman. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10005,6 +10326,13 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après le chien et les balançoires. Une plume vole. On range les chaussures. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa pose rouge et va vers maman. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10495,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10191,7 +10524,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après le chien et les balançoires. Le pain croustille. On met le doudou près de soi. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa dit merci à maman. Papa sourit. On se serre un peu.</t>
+          <t>Léa rejoint le bleu, après le chien et les balançoires. Le pain croustille. On met le doudou près de soi. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa dit merci à maman. Papa sourit. On se serre un peu.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10329,6 +10662,13 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après le chien et les balançoires. Le pain croustille. On met le doudou près de soi. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa dit merci à maman. Papa sourit. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10831,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10515,7 +10860,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après le chien et les balançoires. La laine du doudou est douce. On écoute le cœur, tout doux. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa boit une gorgée. Elle se sent plus légère. On rentre.</t>
+          <t>Léa rejoint le vert, après le chien et les balançoires. La laine du doudou est douce. On écoute le cœur, tout doux. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa boit une gorgée. Elle se sent plus légère. On rentre.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10653,6 +10998,13 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après le chien et les balançoires. La laine du doudou est douce. On écoute le cœur, tout doux. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa boit une gorgée. Elle se sent plus légère. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11167,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11196,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Près de la poule, un rire pas gentil part. Voilà la poule. Un chat miaule une seule fois. Léa pose les pieds par terre, près de maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Près de la poule, un rire pas gentil part. Voilà la poule. Un chat miaule une seule fois. Léa pose les pieds par terre, près de maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11334,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Près de la poule, un rire pas gentil part. Voilà la poule. Un chat miaule une seule fois. Léa pose les pieds par terre, près de maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11155,6 +11518,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Quelqu'un rit d'un camarade. Que fait-on ? Avec la poule.</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11179,7 +11547,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa pose les pieds par terre. On continue, tout calme.</t>
+          <t>Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11321,6 +11689,13 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa pose les pieds par terre. On continue, tout calme.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11882,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11531,7 +11911,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le bac à sable, après la poule. Un papillon passe sans bruit. Le bac à sable est là. Léa pose les mains à vue, loin de l'autre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi le bac à sable, après la poule. Un papillon passe sans bruit. Le bac à sable est là. Léa pose les mains à vue, loin de l'autre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -11669,6 +12049,12 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le bac à sable, après la poule. Un papillon passe sans bruit. Le bac à sable est là. Léa pose les mains à vue, loin de l'autre. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11859,6 +12245,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11883,7 +12274,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après la poule et le bac à sable. Un galet est lisse dans la main. On secoue les mains, loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa pose rouge et va vers maman. La journée continue, tout doux.</t>
+          <t>Léa rejoint le rouge, après la poule et le bac à sable. Un galet est lisse dans la main. On secoue les mains, loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa pose rouge et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12021,6 +12412,13 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après la poule et le bac à sable. Un galet est lisse dans la main. On secoue les mains, loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa pose rouge et va vers maman. La journée continue, tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12581,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12207,7 +12610,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après la poule et le bac à sable. Le train souffle au loin. On pose le sac. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. On se dit à plus tard.</t>
+          <t>Léa rejoint le bleu, après la poule et le bac à sable. Le train souffle au loin. On pose le sac. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. On se dit à plus tard.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12345,6 +12748,13 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après la poule et le bac à sable. Le train souffle au loin. On pose le sac. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa nomme encore le mot, tout bas. On se dit à plus tard.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12917,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12531,7 +12946,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après la poule et le bac à sable. Une vache meugle, loin. On dit le mot de l'émotion. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. Le soleil est encore là.</t>
+          <t>Léa rejoint le vert, après la poule et le bac à sable. Une vache meugle, loin. On dit le mot de l'émotion. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. Le soleil est encore là.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12669,6 +13084,13 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après la poule et le bac à sable. Une vache meugle, loin. On dit le mot de l'émotion. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa serre la main de maman, tout doux. Le soleil est encore là.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13253,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12855,7 +13282,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le toboggan, après la poule. Une cloche sonne au loin. Avec le toboggan, Léa ralentit. Elle écoute maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi le toboggan, après la poule. Une cloche sonne au loin. Avec le toboggan, Léa ralentit. Elle écoute maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -12993,6 +13420,12 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le toboggan, après la poule. Une cloche sonne au loin. Avec le toboggan, Léa ralentit. Elle écoute maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13616,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13207,7 +13645,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après la poule et le toboggan. Un grillon chante, tout petit. On invite d'une petite voix. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. On gardu geste.</t>
+          <t>Léa rejoint le rouge, après la poule et le toboggan. Un grillon chante, tout petit. On invite d'une petite voix. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. On gardu geste.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13345,6 +13783,13 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après la poule et le toboggan. Un grillon chante, tout petit. On invite d'une petite voix. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa serre la main de maman, tout doux. On gardu geste.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13952,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13531,7 +13981,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après la poule et le toboggan. Le bois de la table est lisse. On attend la réponse. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa pose bleu et va vers maman. Papa et maman sont là.</t>
+          <t>Léa rejoint le bleu, après la poule et le toboggan. Le bois de la table est lisse. On attend la réponse. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa pose bleu et va vers maman. Papa et maman sont là.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13669,6 +14119,13 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après la poule et le toboggan. Le bois de la table est lisse. On attend la réponse. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa pose bleu et va vers maman. Papa et maman sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14288,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13855,7 +14317,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après la poule et le toboggan. Une goutte tombe dans l'évier. On propose une autre idée. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. On respire.</t>
+          <t>Léa rejoint le vert, après la poule et le toboggan. Une goutte tombe dans l'évier. On propose une autre idée. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. On respire.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13993,6 +14455,13 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après la poule et le toboggan. Une goutte tombe dans l'évier. On propose une autre idée. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa nomme encore le mot, tout bas. On respire.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14624,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14179,7 +14653,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi les balançoires, après la poule. La corbeille craque. Léa choisit les balançoires. Papa n'est pas loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide.</t>
+          <t>Léa a choisi les balançoires, après la poule. La corbeille craque. Léa choisit les balançoires. Papa n'est pas loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14317,6 +14791,12 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi les balançoires, après la poule. La corbeille craque. Léa choisit les balançoires. Papa n'est pas loin. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14507,6 +14987,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14531,7 +15016,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le rouge, après la poule et les balançoires. Le toboggan est un peu froid. On va vers papa ou maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+          <t>Léa rejoint le rouge, après la poule et les balançoires. Le toboggan est un peu froid. On va vers papa ou maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14669,6 +15154,13 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le rouge, après la poule et les balançoires. Le toboggan est un peu froid. On va vers papa ou maman. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15323,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14855,7 +15352,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le bleu, après la poule et les balançoires. La clochette de la porte tinte. On dit stop, tout clair. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+          <t>Léa rejoint le bleu, après la poule et les balançoires. La clochette de la porte tinte. On dit stop, tout clair. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14993,6 +15490,13 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le bleu, après la poule et les balançoires. La clochette de la porte tinte. On dit stop, tout clair. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15659,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15179,7 +15688,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le vert, après la poule et les balançoires. Ça sent le thym du jardin. On s'éloigne d'un pas. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. On dit : ce n'est pas gentil. Maman aide. Léa pose vert et va vers maman. On se serre un peu.</t>
+          <t>Léa rejoint le vert, après la poule et les balançoires. Ça sent le thym du jardin. On s'éloigne d'un pas. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare. Ce n'est pas gentil. Maman aide. Léa pose vert et va vers maman. On se serre un peu.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15317,6 +15826,13 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le vert, après la poule et les balançoires. Ça sent le thym du jardin. On s'éloigne d'un pas. On ne doit pas rire d'un camarade. On ne doit pas répéter un mot. Ce n'est pas gentil. On répare.
+narrateur|Ce n'est pas gentil. Maman aide.
+narrateur|Léa pose vert et va vers maman. On se serre un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15995,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +16018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16091,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-REL-007.xlsx
+++ b/stories/arbres/TREE-REL-007.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1513,6 +1519,11 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>narrateur|On peut prendre le chat, le chien, ou la poule.</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -1683,6 +1694,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1878,7 @@
           <t>narrateur|Quelqu'un rit d'un camarade. Que fait-on ? Avec le chat.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2039,6 +2052,7 @@
 narrateur|Léa retient le geste. Elle respire.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2230,6 +2244,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2398,6 +2413,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2593,6 +2609,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2762,6 +2779,7 @@
 narrateur|Léa garde le rouge un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2929,6 +2947,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3098,6 +3117,7 @@
 narrateur|Léa est assise. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3265,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3434,6 +3455,7 @@
 narrateur|Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3601,6 +3623,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3793,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3965,6 +3989,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4134,6 +4159,7 @@
 narrateur|Léa dit merci à maman. Papa sourit. On respire.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4301,6 +4327,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4470,6 +4497,7 @@
 narrateur|Léa est près de maman. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4637,6 +4665,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4806,6 +4835,7 @@
 narrateur|Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4973,6 +5003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5141,6 +5172,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5336,6 +5368,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5505,6 +5538,7 @@
 maman|Je t'ai entendu. Papa aussi. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5672,6 +5706,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5841,6 +5876,7 @@
 narrateur|Léa pose bleu et va vers maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6008,6 +6044,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6177,6 +6214,7 @@
 narrateur|Léa garde le vert un instant. Puis elle reprend, calme. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6344,6 +6382,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6512,6 +6551,11 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6693,6 +6737,11 @@
       <c r="AW33" t="inlineStr">
         <is>
           <t>narrateur|Quelqu'un rit d'un camarade. Que fait-on ? Avec le chien.</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
         </is>
       </c>
     </row>
@@ -6868,6 +6917,7 @@
 narrateur|Léa répète le mot. Maman hoche la tête.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7059,6 +7109,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7227,6 +7278,11 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7422,6 +7478,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7591,6 +7648,11 @@
 narrateur|Léa serre la main de maman, tout doux. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7758,6 +7820,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7927,6 +7990,11 @@
 narrateur|Léa garde le bleu un instant. Puis elle reprend, calme. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8094,6 +8162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8263,6 +8332,11 @@
 narrateur|Léa dit merci à maman. Papa sourit. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8430,6 +8504,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8598,6 +8673,11 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8793,6 +8873,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8962,6 +9043,11 @@
 narrateur|Léa nomme encore le mot, tout bas. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9129,6 +9215,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9298,6 +9385,11 @@
 narrateur|Léa boit une gorgée. Elle se sent plus légère. On respire.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9465,6 +9557,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9634,6 +9727,11 @@
 narrateur|Léa garde le vert un instant. Puis elle reprend, calme. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9801,6 +9899,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9969,6 +10068,11 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10164,6 +10268,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10333,6 +10438,11 @@
 narrateur|Léa pose rouge et va vers maman. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10500,6 +10610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10669,6 +10780,11 @@
 narrateur|Léa dit merci à maman. Papa sourit. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10836,6 +10952,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -11005,6 +11122,11 @@
 narrateur|Léa boit une gorgée. Elle se sent plus légère. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>chien_bonjour</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11172,6 +11294,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11340,6 +11463,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11523,6 +11647,7 @@
           <t>narrateur|Quelqu'un rit d'un camarade. Que fait-on ? Avec la poule.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11696,6 +11821,7 @@
 narrateur|Léa pose les pieds par terre. On continue, tout calme.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11887,6 +12013,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12055,6 +12182,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12250,6 +12378,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12419,6 +12548,7 @@
 narrateur|Léa pose rouge et va vers maman. La journée continue, tout doux.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12586,6 +12716,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12755,6 +12886,7 @@
 narrateur|Léa nomme encore le mot, tout bas. On se dit à plus tard.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12922,6 +13054,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13091,6 +13224,7 @@
 narrateur|Léa serre la main de maman, tout doux. Le soleil est encore là.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13258,6 +13392,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13426,6 +13561,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13621,6 +13757,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13790,6 +13927,7 @@
 narrateur|Léa serre la main de maman, tout doux. On gardu geste.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13957,6 +14095,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14126,6 +14265,7 @@
 narrateur|Léa pose bleu et va vers maman. Papa et maman sont là.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14293,6 +14433,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14462,6 +14603,7 @@
 narrateur|Léa nomme encore le mot, tout bas. On respire.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14629,6 +14771,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14797,6 +14940,7 @@
 narrateur|Ce n'est pas gentil. Maman aide.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14992,6 +15136,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15161,6 +15306,7 @@
 narrateur|Léa nomme encore le mot, tout bas. Merci, et au dodo bientôt.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15328,6 +15474,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15497,6 +15644,7 @@
 narrateur|Léa serre la main de maman, tout doux. Le jeu peut recommencer.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15664,6 +15812,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15833,6 +15982,7 @@
 narrateur|Léa pose vert et va vers maman. On se serre un peu.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -16000,6 +16150,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16018,7 +16169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16098,6 +16249,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16112,7 +16277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16299,6 +16464,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
